--- a/survey_templates/039_energy_audit_check_out_form--survey_templates.xlsx
+++ b/survey_templates/039_energy_audit_check_out_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_1</t>
+          <t>energy_usage_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energy usage</t>
+          <t>What time of day do you turn off the lights?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_2</t>
+          <t>energy_usage_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Energy usage</t>
+          <t>Energy-efficient devices at home or office?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_3</t>
+          <t>lighting_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>energy usage</t>
+          <t>Preferred lighting type</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_4</t>
+          <t>electronic_usage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>energy usage</t>
+          <t>Hours spent on electronic devices per day</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_5</t>
+          <t>commute_method</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>energy usage</t>
+          <t>How do you commute?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_6</t>
+          <t>laundry_method</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Energy usage</t>
+          <t>How often do you wash clothes?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_7</t>
+          <t>thermostat_setting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Energy usage</t>
+          <t>Preferred thermostat temperature (winter)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_8</t>
+          <t>solar_panels</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>energy usage</t>
+          <t>Solar panels or other renewable energy sources?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_9</t>
+          <t>water_heater_usage</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Energy usage</t>
+          <t>How often do you use a water heater during winter?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_10</t>
+          <t>energy_efficient_appliances</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>energy usage</t>
+          <t>Energy-efficient appliances?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_11</t>
+          <t>electricity_bill</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Energy usage</t>
+          <t>Average electricity bill per month</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_12</t>
+          <t>renewable_energy_plans</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>energy usage</t>
+          <t>Plans to switch to renewable energy sources?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_1_choices</t>
+          <t>energy_usage_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_1_choices</t>
+          <t>energy_usage_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -861,168 +861,389 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_2_choices</t>
+          <t>lighting_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>led</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>LED</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_2_choices</t>
+          <t>lighting_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>incandescent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Incandescent</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_2_choices</t>
+          <t>lighting_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>halogen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Halogen</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_6_choices</t>
+          <t>commute_method_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_6_choices</t>
+          <t>commute_method_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_6_choices</t>
+          <t>laundry_method_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>always_use_an_energy-intensive_washing_machine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Always use an energy-intensive washing machine</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_7_choices</t>
+          <t>laundry_method_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sometimes_use_an_energy-intensive_washing_machine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sometimes use an energy-intensive washing machine</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_7_choices</t>
+          <t>laundry_method_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rarely_use_an_energy-intensive_washing_machine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Rarely use an energy-intensive washing machine</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_11_choices</t>
+          <t>laundry_method_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>always_hand-wash_or_air-dry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Always hand-wash or air-dry</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>energy_audit_check_out_form_11_choices</t>
+          <t>thermostat_setting_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>60-64°f_(15-18°c)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
+        <is>
+          <t>60-64°F (15-18°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>thermostat_setting_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>65-69°f_(18-21°c)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>65-69°F (18-21°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>thermostat_setting_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>70-74°f_(21-23°c)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>70-74°F (21-23°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>thermostat_setting_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>75-79°f_(24-26°c)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>75-79°F (24-26°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>solar_panels_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>solar_panels_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>water_heater_usage_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>frequently</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Frequently</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>water_heater_usage_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>water_heater_usage_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>water_heater_usage_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>energy_efficient_appliances_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>energy_efficient_appliances_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>renewable_energy_plans_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>renewable_energy_plans_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
